--- a/baseline/test_report.xlsx
+++ b/baseline/test_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestLogTable" displayName="TestLogTable" ref="A1:P17" headerRowCount="1">
-  <autoFilter ref="A1:P17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestLogTable" displayName="TestLogTable" ref="A1:P111" headerRowCount="1">
+  <autoFilter ref="A1:P111"/>
   <tableColumns count="16">
     <tableColumn id="1" name="RunID"/>
     <tableColumn id="2" name="Timestamp"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -446,17 +446,17 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="49" customWidth="1" min="16" max="16"/>
+    <col width="51" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,12 +544,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-30T10:53:28</t>
+          <t>2026-04-20T15:59:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Import nominations</t>
+          <t>Import CSV</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -583,41 +583,21 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step2_import\01_nominations_landing.png</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step2_import\02_import_modal_open.png</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step2_import\04_click_upload.png</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step2_import\05_after_upload_on_week.png</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step2_import</t>
+          <t>artifacts\20260420-155931\step01_import</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-30T10:53:45</t>
+          <t>2026-04-20T15:59:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -626,19 +606,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Profiles baseline</t>
+          <t>Baseline Nominations</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -651,26 +631,21 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step3_profiles_before\01_profiles_baseline.png</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step3_profiles_before</t>
+          <t>artifacts\20260420-155931\step02_nominations</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:00</t>
+          <t>2026-04-20T15:59:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -679,10 +654,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -691,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Occupancy Check</t>
+          <t>Profiles Check</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,24 +681,24 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step3_profiles_before\zz_occupancy_at_step_3.png</t>
+          <t>artifacts\20260420-155931\step03_profiles\zz_profiles.png</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step3_profiles_before</t>
+          <t>artifacts\20260420-155931\step03_profiles</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:04</t>
+          <t>2026-04-20T16:00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,19 +707,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confirm blue slot</t>
+          <t>Occupancy Check</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -757,36 +732,26 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_01\01_modal_open.png</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_01\03_after_click.png</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_01\04_after_close.png</t>
+          <t>artifacts\20260420-155931\step04_occupancy\zz_occupancy_at_step_4.png</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_01</t>
+          <t>artifacts\20260420-155931\step04_occupancy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:07</t>
+          <t>2026-04-20T16:00:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -795,10 +760,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,7 +772,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confirm blue slot</t>
+          <t>Costs Breakdown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -820,36 +785,26 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_02\01_modal_open.png</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_02\03_after_click.png</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_02\04_after_close.png</t>
+          <t>artifacts\20260420-155931\step05_costs\zz_costs_breakdown_w18.png</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_02</t>
+          <t>artifacts\20260420-155931\step05_costs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:09</t>
+          <t>2026-04-20T16:00:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -858,19 +813,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Confirm blue slot</t>
+          <t>Confirm slot #1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -885,34 +840,34 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_03\01_modal_open.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_01\01_modal_open.png</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_03\03_after_click.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_01\03_after_click.png</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_03\04_after_close.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_01\04_after_close.png</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_03</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:12</t>
+          <t>2026-04-20T16:00:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -921,19 +876,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Confirm blue slot</t>
+          <t>Confirm slot #2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -948,34 +903,34 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_04\01_modal_open.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_02\01_modal_open.png</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_04\03_after_click.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_02\03_after_click.png</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_04\04_after_close.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_02\04_after_close.png</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_04</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:15</t>
+          <t>2026-04-20T16:00:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -984,19 +939,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Confirm blue slot</t>
+          <t>Confirm slot #3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1011,34 +966,34 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_05\01_modal_open.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_03\01_modal_open.png</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_05\03_after_click.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_03\03_after_click.png</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_05\04_after_close.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_03\04_after_close.png</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\slot_05</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:18</t>
+          <t>2026-04-20T16:00:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1047,19 +1002,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nominations after confirm</t>
+          <t>Confirm slot #4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1072,26 +1027,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_04\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_04\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\zz_nominations_after_confirm.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_04\04_after_close.png</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:36</t>
+          <t>2026-04-20T16:00:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1100,19 +1065,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Profiles after confirm</t>
+          <t>Confirm slot #5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1125,26 +1090,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_05\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_05\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\zz_profiles_after_confirm_5slots.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_05\04_after_close.png</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:51</t>
+          <t>2026-04-20T16:00:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1153,19 +1128,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Occupancy Check</t>
+          <t>Confirm slot #6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1178,26 +1153,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_06\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_06\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm\zz_occupancy_at_step_5.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_06\04_after_close.png</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step5_confirm</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-01-30T10:54:56</t>
+          <t>2026-04-20T16:00:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1206,10 +1191,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1218,7 +1203,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nominations after reject</t>
+          <t>Confirm slot #7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1231,26 +1216,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_07\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_07\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject\zz_nominations_after_reject.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_07\04_after_close.png</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-01-30T10:55:14</t>
+          <t>2026-04-20T16:00:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1271,7 +1266,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Profiles after reject</t>
+          <t>Confirm slot #8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1284,26 +1279,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_08\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_08\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject\zz_profiles_after_reject_0slots.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_08\04_after_close.png</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-01-30T10:55:29</t>
+          <t>2026-04-20T16:00:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1324,7 +1329,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Occupancy Check</t>
+          <t>Confirm slot #9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1337,26 +1342,36 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_09\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_09\03_after_click.png</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject\zz_occupancy_at_step_6.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_09\04_after_close.png</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step6_reject</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-01-30T10:55:39</t>
+          <t>2026-04-20T16:00:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1365,19 +1380,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Step 7</t>
+          <t>Step 6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Confirm Week &amp; Final Profiles</t>
+          <t>Confirm slot #10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1390,31 +1405,36 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | </t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_10\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_10\03_after_click.png</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step7_final_check\02_final_profiles_check.png</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_10\04_after_close.png</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>artifacts\20260130-105304\step7_final_check</t>
+          <t>artifacts\20260420-155931\step06_confirm\slot_10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260130-105304</t>
+          <t>20260420-155931</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-01-30T10:55:54</t>
+          <t>2026-04-20T16:00:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1423,39 +1443,5831 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Confirm slot #11</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_11\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_11\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_11\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:00:37</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Confirm slot #12</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_12\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_12\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_12\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:00:39</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Confirm slot #13</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_13\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_13\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_13\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:00:41</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Confirm slot #14</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_14\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_14\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_14\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:00:43</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Confirm slot #15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_15\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_15\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_15\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step06_confirm\slot_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:00:48</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Step 7</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Profiles Check</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step07_profiles\zz_profiles.png</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step07_profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Step 8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Occupancy Check</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step7_final_check\zz_occupancy_at_step_7.png</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>artifacts\20260130-105304\step7_final_check</t>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step08_occupancy\zz_occupancy_at_step_8.png</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step08_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Step 9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Costs Breakdown</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step09_costs\zz_costs_breakdown_w18.png</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step09_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Reject slot #1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_01\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_01\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_01\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Reject slot #2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_02\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_02\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_02\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Reject slot #3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_03\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_03\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_03\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Reject slot #4</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_04\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_04\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_04\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reject slot #5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_05\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_05\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_05\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_05</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Reject slot #6</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_06\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_06\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_06\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Reject slot #7</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_07\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_07\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_07\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:32</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Reject slot #8</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_08\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_08\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_08\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Reject slot #9</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_09\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_09\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_09\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:37</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Reject slot #10</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_10\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_10\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_10\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:39</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Reject slot #11</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_11\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_11\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_11\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:40</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Reject slot #12</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_12\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_12\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_12\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:42</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Reject slot #13</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_13\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_13\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_13\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Reject slot #14</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_14\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_14\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_14\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:47</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Reject slot #15</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_15\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_15\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_15\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:49</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Reject slot #16</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_16\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_16\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_16\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:52</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Reject slot #17</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_17\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_17\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_17\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Reject slot #18</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_18\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_18\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_18\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:56</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Reject slot #19</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_19\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_19\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_19\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:01:58</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Reject slot #20</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_20\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_20\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_20\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>18</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Reject slot #21</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_21\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_21\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_21\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:02</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>18</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Reject slot #22</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_22\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_22\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_22\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Reject slot #23</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_23\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_23\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_23\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:06</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>18</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Reject slot #24</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_24\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_24\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_24\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>18</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Reject slot #25</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_25\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_25\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_25\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>18</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Reject slot #26</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_26\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_26\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_26\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Reject slot #27</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_27\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_27\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_27\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:14</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Reject slot #28</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_28\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_28\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_28\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:16</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>18</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Reject slot #29</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_29\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_29\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_29\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:18</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>18</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Reject slot #30</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_30\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_30\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_30\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:20</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Reject slot #31</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_31\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_31\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_31\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_31</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:22</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>18</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Reject slot #32</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_32\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_32\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_32\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_32</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>18</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Reject slot #33</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_33\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_33\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_33\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_33</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>18</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Reject slot #34</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_34\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_34\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_34\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_34</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:28</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Reject slot #35</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_35\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_35\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_35\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_35</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>18</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Reject slot #36</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_36\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_36\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_36\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_36</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:32</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>18</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Reject slot #37</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_37\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_37\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_37\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_37</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:34</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>18</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Reject slot #38</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_38\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_38\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_38\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_38</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:36</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>18</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Reject slot #39</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_39\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_39\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_39\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:38</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>18</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Reject slot #40</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_40\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_40\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_40\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_40</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>18</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Reject slot #41</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_41\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_41\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_41\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_41</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:42</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>18</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Reject slot #42</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_42\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_42\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_42\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_42</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:44</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>18</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Reject slot #43</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_43\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_43\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_43\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_43</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:46</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>18</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Reject slot #44</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_44\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_44\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_44\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_44</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:48</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>18</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Reject slot #45</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_45\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_45\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_45\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_45</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:50</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>18</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Reject slot #46</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_46\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_46\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_46\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_46</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:52</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>18</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Reject slot #47</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_47\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_47\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_47\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_47</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:54</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>18</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Reject slot #48</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_48\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_48\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_48\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_48</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:57</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>18</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Reject slot #49</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_49\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_49\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_49\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_49</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:02:59</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>18</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Reject slot #50</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_50\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_50\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_50\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_50</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>18</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Reject slot #51</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_51\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_51\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_51\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_51</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>18</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Reject slot #52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_52\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_52\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_52\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_52</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>18</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Reject slot #53</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_53\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_53\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_53\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_53</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:07</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>18</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Reject slot #54</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_54\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_54\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_54\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_54</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:09</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>18</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Reject slot #55</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_55\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_55\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_55\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_55</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:11</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>18</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Reject slot #56</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_56\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_56\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_56\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_56</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:13</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>18</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Reject slot #57</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_57\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_57\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_57\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_57</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:15</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Reject slot #58</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_58\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_58\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_58\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_58</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>18</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Reject slot #59</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_59\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_59\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_59\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_59</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:19</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>18</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Reject slot #60</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_60\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_60\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_60\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_60</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:22</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>18</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Reject slot #61</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_61\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_61\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_61\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_61</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>18</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Reject slot #62</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_62\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_62\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_62\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_62</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>18</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Reject slot #63</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_63\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_63\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_63\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_63</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:28</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>18</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Reject slot #64</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_64\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_64\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_64\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_64</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>18</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Reject slot #65</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_65\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_65\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_65\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_65</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>18</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Reject slot #66</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_66\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_66\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_66\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_66</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>18</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Reject slot #67</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_67\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_67\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_67\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_67</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:37</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>18</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Reject slot #68</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_68\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_68\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_68\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_68</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:39</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>18</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Reject slot #69</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_69\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_69\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_69\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_69</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:41</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>18</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Reject slot #70</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_70\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_70\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_70\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_70</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:43</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>18</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Reject slot #71</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_71\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_71\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_71\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_71</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:45</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>18</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Reject slot #72</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_72\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_72\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_72\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_72</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:47</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>18</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Reject slot #73</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_73\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_73\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_73\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_73</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:49</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>18</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Reject slot #74</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_74\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_74\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_74\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_74</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:51</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>18</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Reject slot #75</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_75\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_75\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_75\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_75</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:53</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>18</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Reject slot #76</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_76\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_76\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_76\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_76</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:03:55</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>18</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Reject slot #77</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_77\01_modal_open.png</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_77\03_after_click.png</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_77\04_after_close.png</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step10_reject\slot_77</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>18</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Step 11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Profiles Check</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step11_profiles\zz_profiles.png</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step11_profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:14</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>18</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Step 12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Occupancy Check</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step12_occupancy\zz_occupancy_at_step_12.png</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step12_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>18</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Step 13</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Costs Breakdown</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step13_costs\zz_costs_breakdown_w18.png</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step13_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:29</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>18</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Step 14</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Add Maintenance (High Pressure Compressor)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step14_maintenance_tues\04_maintenance_done.png</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step14_maintenance_tues</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:33</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>18</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Step 15</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Add Maintenance (Stack 1)</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step15_maintenance_thu\04_maintenance_done.png</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step15_maintenance_thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:36</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>18</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Step 16</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Add Maintenance (Loading Bay 1)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step16_maintenance_week\04_maintenance_done.png</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step16_maintenance_week</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:41</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>18</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Step 17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Confirm Week (bulk)</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step17_confirm_week</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:45</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>18</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Step 18</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Profiles Check</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step18_profiles_post\zz_profiles.png</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step18_profiles_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:04:59</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>18</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Step 19</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Occupancy Check</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step19_occupancy_post\zz_occupancy_at_step_19.png</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step19_occupancy_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20260420-155931</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:05:04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>18</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Step 20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Reject Week (bulk)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>artifacts\20260420-155931\step20_reject_week</t>
         </is>
       </c>
     </row>
